--- a/processo_2/synthetic_proposals/PROPOSTA_031/ficha_pontuacao.xlsx
+++ b/processo_2/synthetic_proposals/PROPOSTA_031/ficha_pontuacao.xlsx
@@ -546,13 +546,13 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>7</v>
       </c>
       <c r="F6" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="G6" t="inlineStr"/>
     </row>
@@ -638,13 +638,13 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
         <v>1.5</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="G10" t="inlineStr"/>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -703,7 +703,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -726,7 +726,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -749,7 +749,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -799,17 +799,9 @@
     </row>
     <row r="18">
       <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Revista Científica Avançada 1</t>
-        </is>
-      </c>
+      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>72%</t>
-        </is>
-      </c>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
@@ -916,13 +908,13 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
         <v>5</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G24" t="inlineStr"/>
     </row>
@@ -939,13 +931,13 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E25" t="n">
         <v>3</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G25" t="inlineStr"/>
     </row>
@@ -958,7 +950,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -981,7 +973,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1050,7 +1042,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>sem teto</t>
+          <t>10</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1075,7 +1067,7 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="n">
-        <v>7</v>
+        <v>9.5</v>
       </c>
       <c r="G31" t="inlineStr"/>
     </row>
@@ -1118,17 +1110,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
         <v>1</v>
       </c>
       <c r="F34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G34" t="inlineStr"/>
     </row>
@@ -1141,17 +1133,17 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
         <v>2</v>
       </c>
       <c r="F35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G35" t="inlineStr"/>
     </row>
@@ -1187,17 +1179,17 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
         <v>10</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G37" t="inlineStr"/>
     </row>
@@ -1210,7 +1202,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1233,7 +1225,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1256,17 +1248,17 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E40" t="n">
         <v>3</v>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G40" t="inlineStr"/>
     </row>
@@ -1279,17 +1271,17 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E41" t="n">
         <v>3</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G41" t="inlineStr"/>
     </row>
@@ -1302,7 +1294,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1325,7 +1317,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1369,13 +1361,13 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
         <v>2</v>
       </c>
       <c r="F45" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G45" t="inlineStr"/>
     </row>
@@ -1543,17 +1535,17 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E53" t="n">
         <v>5</v>
       </c>
       <c r="F53" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G53" t="inlineStr"/>
     </row>
@@ -1566,17 +1558,17 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E54" t="n">
         <v>2</v>
       </c>
       <c r="F54" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G54" t="inlineStr"/>
     </row>
@@ -1612,7 +1604,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -1635,17 +1627,17 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>sem teto</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E57" t="n">
         <v>2</v>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G57" t="inlineStr"/>
     </row>
@@ -1660,7 +1652,7 @@
       <c r="D58" t="inlineStr"/>
       <c r="E58" t="inlineStr"/>
       <c r="F58" t="n">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="G58" t="inlineStr"/>
     </row>
@@ -1776,13 +1768,13 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E64" t="n">
         <v>4</v>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G64" t="inlineStr"/>
     </row>
@@ -1843,7 +1835,7 @@
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G67" t="inlineStr"/>
     </row>
@@ -1858,7 +1850,7 @@
       <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="n">
-        <v>24</v>
+        <v>51.5</v>
       </c>
       <c r="G68" t="inlineStr"/>
     </row>
